--- a/bizconfig/static-xlsx/moba/pixel_moba/hero_profiles.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/hero_profiles.xlsx
@@ -413,76 +413,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>hero_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>max_level</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>start_gold</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>respawn_base_sec</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>respawn_per_level_sec</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>skill_q_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>skill_w_id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>skill_e_id</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>skill_r_id</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>r_unlock_level</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>passive_skill_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>base_attack_bonus</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>lore</t>
         </is>
@@ -496,65 +518,70 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -568,65 +595,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>notnull&amp;only</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
@@ -695,10 +727,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>!s!c</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>!s</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>!c</t>
         </is>
@@ -707,70 +744,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>主键:与 hero_id 同值(每 hero 一行 profile)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>外键 -&gt; unit.id</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>英雄定位: archer/warrior/mage</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>最大等级(固定 10)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>初始金币</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>基础复活时间秒</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>每死亡等级加复活秒数</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Q技能ID,外键 -&gt; skill.id</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>W技能ID,外键 -&gt; skill.id</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>E技能ID,外键 -&gt; skill.id</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>R大招ID,外键 -&gt; skill.id</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>R大招解锁等级(通常 6)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>被动技能ID,外键 -&gt; skill.id,无则留空</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>基础攻击加成(远程/近战修正),仅服务端</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>英雄背景故事(客户端 tooltip)</t>
         </is>
@@ -780,45 +822,48 @@
       <c r="A6" t="n">
         <v>1001</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>warrior</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>500</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>5001</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>5002</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5003</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5004</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>5005</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>近战战士,擅长冲锋与控制</t>
         </is>
@@ -828,45 +873,48 @@
       <c r="A7" t="n">
         <v>1002</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>mage</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>500</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>5011</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>5012</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5013</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5014</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>6</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>5015</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>远程法师,高爆发魔法伤害</t>
         </is>
@@ -876,45 +924,48 @@
       <c r="A8" t="n">
         <v>1003</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>archer</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>500</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5021</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>5022</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5023</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>5024</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>5025</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>远程弓手,持续物理输出</t>
         </is>
